--- a/Project_Group_Formation_Structured_Evaluation.xlsx
+++ b/Project_Group_Formation_Structured_Evaluation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git Backup\2GITHUB\AEC_ML_Batch_1_August_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27A72E7-2CD8-459E-83F6-373909FC0AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43C5C0F-53C7-4132-A40E-46669A9C1FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="318">
   <si>
     <t>Evaluation scheme: Project Design &amp; Implementation (40) + Presentation &amp; Demonstration (30) + Viva / Technical Understanding (30) = 100</t>
   </si>
@@ -1058,6 +1058,9 @@
   </si>
   <si>
     <t>PROJECT GROUP FORMATION &amp; EVALUATION (Batch-2)</t>
+  </si>
+  <si>
+    <t>This attached MS-Excel file contains project group formation information. Can you please make this one structured? Also add four columns extra so that during project presentation and evaluation, we can put marks and calculate total marks also. Give the necessary column headings and do the needful as well.</t>
   </si>
 </sst>
 </file>
@@ -3750,7 +3753,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -4773,6 +4776,11 @@
       <c r="AA16" s="5"/>
       <c r="AB16" s="13"/>
     </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>317</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:AB1"/>

--- a/Project_Group_Formation_Structured_Evaluation.xlsx
+++ b/Project_Group_Formation_Structured_Evaluation.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git Backup\2GITHUB\AEC_ML_Batch_1_August_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43C5C0F-53C7-4132-A40E-46669A9C1FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53171F40-6136-474F-9E15-4BB405E71835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Groups" sheetId="1" r:id="rId1"/>
     <sheet name="Student Roster" sheetId="2" r:id="rId2"/>
-    <sheet name="Original Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Evaluation Guide" sheetId="4" r:id="rId3"/>
+    <sheet name="Original Data" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="360">
   <si>
     <t>Evaluation scheme: Project Design &amp; Implementation (40) + Presentation &amp; Demonstration (30) + Viva / Technical Understanding (30) = 100</t>
   </si>
@@ -1062,12 +1063,138 @@
   <si>
     <t>This attached MS-Excel file contains project group formation information. Can you please make this one structured? Also add four columns extra so that during project presentation and evaluation, we can put marks and calculate total marks also. Give the necessary column headings and do the needful as well.</t>
   </si>
+  <si>
+    <t>PROJECT EVALUATION GUIDE</t>
+  </si>
+  <si>
+    <t>Enter marks only in the yellow cells on the Project Groups sheet. Total marks are calculated automatically after all three criteria are entered.</t>
+  </si>
+  <si>
+    <t>Assessment Criterion</t>
+  </si>
+  <si>
+    <t>Maximum Marks</t>
+  </si>
+  <si>
+    <t>What to Evaluate</t>
+  </si>
+  <si>
+    <t>Suggested Scoring Reference</t>
+  </si>
+  <si>
+    <t>Project Quality &amp; Implementation</t>
+  </si>
+  <si>
+    <t>Problem relevance, data preparation, methodology, solution or model design, correctness, functionality, completeness and implementation quality.</t>
+  </si>
+  <si>
+    <t>Excellent: 34–40 | Good: 28–33 | Satisfactory: 20–27 | Needs improvement: 0–19</t>
+  </si>
+  <si>
+    <t>Presentation &amp; Demonstration</t>
+  </si>
+  <si>
+    <t>Logical structure, clarity, visual quality, time management, balanced participation and successful demonstration of results.</t>
+  </si>
+  <si>
+    <t>Excellent: 26–30 | Good: 21–25 | Satisfactory: 15–20 | Needs improvement: 0–14</t>
+  </si>
+  <si>
+    <t>Viva / Technical Understanding</t>
+  </si>
+  <si>
+    <t>Conceptual depth, technical justification, ability to answer questions, individual ownership, limitations and future scope.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>The total is the sum of all three assessment criteria.</t>
+  </si>
+  <si>
+    <t>Calculated automatically in the Project Groups sheet.</t>
+  </si>
+  <si>
+    <t>OVERALL PERFORMANCE BANDS</t>
+  </si>
+  <si>
+    <t>Total Marks</t>
+  </si>
+  <si>
+    <t>Performance Band</t>
+  </si>
+  <si>
+    <t>General Interpretation</t>
+  </si>
+  <si>
+    <t>Suggested Action</t>
+  </si>
+  <si>
+    <t>85–100</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Outstanding project quality and strong technical ownership.</t>
+  </si>
+  <si>
+    <t>Recognize as exemplary work.</t>
+  </si>
+  <si>
+    <t>70–84</t>
+  </si>
+  <si>
+    <t>Very Good</t>
+  </si>
+  <si>
+    <t>Strong work with only minor gaps.</t>
+  </si>
+  <si>
+    <t>Provide targeted refinement feedback.</t>
+  </si>
+  <si>
+    <t>55–69</t>
+  </si>
+  <si>
+    <t>Good / Satisfactory</t>
+  </si>
+  <si>
+    <t>Core requirements met with visible improvement areas.</t>
+  </si>
+  <si>
+    <t>Recommend specific improvements.</t>
+  </si>
+  <si>
+    <t>40–54</t>
+  </si>
+  <si>
+    <t>Needs Improvement</t>
+  </si>
+  <si>
+    <t>Partial understanding or incomplete execution.</t>
+  </si>
+  <si>
+    <t>Require corrective improvements.</t>
+  </si>
+  <si>
+    <t>Below 40</t>
+  </si>
+  <si>
+    <t>Unsatisfactory</t>
+  </si>
+  <si>
+    <t>Major deficiencies in execution, presentation or understanding.</t>
+  </si>
+  <si>
+    <t>Consider re-evaluation after revision.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1108,8 +1235,32 @@
       <color rgb="FF1F4E78"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="17"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1166,6 +1317,11 @@
         <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F75B5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1179,7 +1335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1227,6 +1383,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1319,6 +1496,30 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3E7909A3-DFF3-4442-BFD1-23B55FBFEFE1}" name="EvaluationCriteriaTable" displayName="EvaluationCriteriaTable" ref="A4:D8" totalsRowShown="0">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{9776AD96-06F8-4AB0-B1AC-96C575A908C6}" name="Assessment Criterion"/>
+    <tableColumn id="2" xr3:uid="{B5365260-544E-40B9-84A2-EED9199FEB18}" name="Maximum Marks"/>
+    <tableColumn id="3" xr3:uid="{14B93376-1912-4415-92B7-6F9FA212FD65}" name="What to Evaluate"/>
+    <tableColumn id="4" xr3:uid="{C10EC34F-D86C-41EE-BD7B-F6EDA70FD978}" name="Suggested Scoring Reference"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{8CDBF5FF-BFAA-41B1-A2F8-59AFF34839DB}" name="PerformanceBandsTable" displayName="PerformanceBandsTable" ref="A11:D16" totalsRowShown="0">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{8CDD5E57-5206-4B2C-86F6-147E31FF5F5F}" name="Total Marks"/>
+    <tableColumn id="2" xr3:uid="{73A0AC42-2275-47C0-B66B-F10E7A1672A9}" name="Performance Band"/>
+    <tableColumn id="3" xr3:uid="{6DFA5B94-FAF4-45FF-B6E6-823FF02B0508}" name="General Interpretation"/>
+    <tableColumn id="4" xr3:uid="{0418E025-5A8F-43E2-ABAA-0819F7B64F70}" name="Suggested Action"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OriginalDataTable" displayName="OriginalDataTable" ref="A4:AB16" totalsRowShown="0">
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Enter Department"/>
@@ -3752,6 +3953,209 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F64758A-015B-46BA-820C-1A9C3BB9FB0C}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="24" customHeight="1">
+      <c r="A1" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+    </row>
+    <row r="2" spans="1:4" ht="28.8" customHeight="1">
+      <c r="A2" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+    </row>
+    <row r="4" spans="1:4" ht="27.15" customHeight="1">
+      <c r="A4" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="49.65" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B5" s="6">
+        <v>40</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="49.65" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B6" s="6">
+        <v>30</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="49.65" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B7" s="6">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="28.05" customHeight="1">
+      <c r="A8" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="B8" s="21">
+        <v>100</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19.2" customHeight="1">
+      <c r="A10" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="11" spans="1:4" ht="25.65" customHeight="1">
+      <c r="A11" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="38.4" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="38.4" customHeight="1">
+      <c r="A13" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="38.4" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="38.4" customHeight="1">
+      <c r="A15" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="38.4" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:D10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
